--- a/docs/product/report-templates/school-journal-full.xlsx
+++ b/docs/product/report-templates/school-journal-full.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Serg\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\AI_Agents\classroom-agent\docs\product\report-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,15 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Облік проведення занять, їх відвідування та успішність студентів</t>
   </si>
   <si>
     <t>(назва навчальної дисципліни/предмета)</t>
-  </si>
-  <si>
-    <t>Кількість годин на _________ семестр _______________________________</t>
   </si>
   <si>
     <t>Дата проведення заняття</t>
@@ -64,6 +61,12 @@
   </si>
   <si>
     <t>Підпис викладача</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кількість годин на </t>
+  </si>
+  <si>
+    <t>семестр</t>
   </si>
 </sst>
 </file>
@@ -650,12 +653,14 @@
     </row>
     <row r="5" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -710,7 +715,7 @@
       <c r="A7" s="3"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -738,10 +743,10 @@
     </row>
     <row r="8" spans="1:28" ht="72.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
@@ -28656,28 +28661,28 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="12"/>
+    </row>
+    <row r="3" spans="1:6" s="20" customFormat="1" ht="48.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="12"/>
-    </row>
-    <row r="3" spans="1:6" s="20" customFormat="1" ht="48.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="C3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="F3" s="18" t="s">
         <v>11</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
